--- a/data/input/DOC_20260113_AR99.xlsx
+++ b/data/input/DOC_20260113_AR99.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\sosiknas1.whoi.edu\Lab_data\LTER\DOC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC329EA-6AD0-4708-BCC9-526399FA5B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395977CD-F281-41BF-9CDA-BEC7A03E5A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="2190" windowWidth="24945" windowHeight="13785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -187,6 +187,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -285,7 +286,7 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -736,10 +737,10 @@
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" s="15">
         <v>46134</v>
@@ -784,10 +785,10 @@
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" s="15">
         <v>46134</v>
@@ -832,10 +833,10 @@
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" s="15">
         <v>46134</v>
@@ -880,10 +881,10 @@
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5" s="15">
         <v>46134</v>
@@ -928,10 +929,10 @@
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6" s="15">
         <v>46134</v>
@@ -976,10 +977,10 @@
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" s="15">
         <v>46134</v>
@@ -1024,10 +1025,10 @@
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" s="15">
         <v>46134</v>
@@ -1072,10 +1073,10 @@
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" s="15">
         <v>46134</v>
@@ -1122,10 +1123,10 @@
         <v>23</v>
       </c>
       <c r="L10" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" s="15">
         <v>46134</v>
@@ -1170,10 +1171,10 @@
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" s="15">
         <v>46134</v>
@@ -1220,10 +1221,10 @@
         <v>23</v>
       </c>
       <c r="L12" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" s="15">
         <v>46134</v>
@@ -1268,10 +1269,10 @@
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="15">
         <v>46134</v>
@@ -1316,10 +1317,10 @@
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="15">
         <v>46134</v>
@@ -1364,10 +1365,10 @@
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" s="15">
         <v>46134</v>
@@ -1412,10 +1413,10 @@
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" s="15">
         <v>46134</v>
@@ -1460,10 +1461,10 @@
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17" s="15">
         <v>46134</v>
@@ -1510,10 +1511,10 @@
         <v>23</v>
       </c>
       <c r="L18" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O18" s="15">
         <v>46134</v>
@@ -1558,10 +1559,10 @@
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" s="15">
         <v>46134</v>
@@ -1606,10 +1607,10 @@
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" s="15">
         <v>46134</v>
@@ -1654,10 +1655,10 @@
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" s="15">
         <v>46134</v>
@@ -1702,10 +1703,10 @@
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O22" s="15">
         <v>46134</v>
@@ -1750,10 +1751,10 @@
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" s="15">
         <v>46134</v>
@@ -1798,10 +1799,10 @@
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="15">
         <v>46134</v>
@@ -1848,10 +1849,10 @@
         <v>23</v>
       </c>
       <c r="L25" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O25" s="15">
         <v>46134</v>
@@ -1896,10 +1897,10 @@
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O26" s="15">
         <v>46134</v>
@@ -1944,10 +1945,10 @@
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O27" s="15">
         <v>46134</v>
@@ -1992,10 +1993,10 @@
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" s="15">
         <v>46134</v>
@@ -2040,10 +2041,10 @@
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M29" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O29" s="15">
         <v>46134</v>
@@ -2088,10 +2089,10 @@
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" s="15">
         <v>46134</v>
@@ -2136,10 +2137,10 @@
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" s="15">
         <v>46134</v>
@@ -2184,10 +2185,10 @@
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" s="15">
         <v>46134</v>
@@ -2232,10 +2233,10 @@
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33" s="15">
         <v>46134</v>
@@ -2280,10 +2281,10 @@
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O34" s="15">
         <v>46134</v>
@@ -2337,11 +2338,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="e362b6aa-9e52-454d-a744-a011f894490f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2527,26 +2529,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="e362b6aa-9e52-454d-a744-a011f894490f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EBAD766-690B-4B4D-8BA3-45BBCD0E4195}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C56E6CDE-B1D8-4B8C-A235-CFA6F399302F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="e362b6aa-9e52-454d-a744-a011f894490f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2570,9 +2563,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C56E6CDE-B1D8-4B8C-A235-CFA6F399302F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EBAD766-690B-4B4D-8BA3-45BBCD0E4195}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="e362b6aa-9e52-454d-a744-a011f894490f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>